--- a/DarkDestroyer_20220420_2017.3.0f3/Assets/99 说明/1201 配置地图怪物/map_v2.xlsx
+++ b/DarkDestroyer_20220420_2017.3.0f3/Assets/99 说明/1201 配置地图怪物/map_v2.xlsx
@@ -1,57 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="map_format" type="4" refreshedVersion="0" background="1">
-    <webPr xml="1" sourceData="1" url="D:\Dev\SyncRes\ResDarkGod\xls\map_format.xml" htmlTables="1" htmlFormat="all"/>
+  <connection id="1" name="map_format" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\Dev\SyncRes\ResDarkGod\xls\map_format.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
-  <connection id="2" name="map_format_v2" type="4" refreshedVersion="0" background="1">
-    <webPr xml="1" sourceData="1" url="D:\Dev\SyncMake\MK_DarkGod\Client\Assets\Resources\ResCfgs\map.xml" htmlTables="1" htmlFormat="all"/>
+  <connection id="2" name="map_format_v2" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\Dev\SyncMake\MK_DarkGod\Client\Assets\Resources\ResCfgs\map.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
-  <connection id="3" name="map_format1" type="4" refreshedVersion="0" background="1">
-    <webPr xml="1" sourceData="1" url="D:\Dev\SyncMake\MK_DarkGod\Client\Assets\Resources\ResCfgs\map.xml" htmlTables="1" htmlFormat="all"/>
+  <connection id="3" name="map_format1" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\Dev\SyncMake\MK_DarkGod\Client\Assets\Resources\ResCfgs\map.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="31">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>mapName</t>
+  </si>
   <si>
     <t>sceneName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mainCamPos</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mainCamRote</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>playerBornPos</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>playerBornRote</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monsterLst</t>
   </si>
   <si>
     <t>10000</t>
@@ -63,6 +66,9 @@
     <t>SceneMainCity</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>17.4,7,50</t>
   </si>
   <si>
@@ -75,55 +81,25 @@
     <t>0,0,0</t>
   </si>
   <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>荒野遗迹</t>
+  </si>
+  <si>
+    <t>SceneOrge</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>-13.19,18.87,14.69</t>
   </si>
   <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>10002</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>10004</t>
-  </si>
-  <si>
-    <t>10005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10006</t>
+    <t>-10,13.2,11.5</t>
   </si>
   <si>
     <t>0,145,0</t>
-  </si>
-  <si>
-    <t>-10,13.2,11.5</t>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mapName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monsterLst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒野遗迹</t>
-  </si>
-  <si>
-    <t>SceneOrge</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>#|1001,-4.39,13.14,3.79,-50
@@ -136,6 +112,33 @@
  |1001,15.38,8.8,40.7,173.3
  |1001,9,8.9,38.6,145.5
  |2001,11.4,8.85,41,142</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>10005</t>
+  </si>
+  <si>
+    <t>10006</t>
+  </si>
+  <si>
+    <t>#|1001,-4.39,13.3,3.79,-50
+ |1001,-7.55,13.3, 3,0
+#|1001,18.86,13.6,3.7,-107.3
+ |1001,14.35,13.35,5.95,-117.4
+ |1001,15.11,13.35,1.63,-66.1
+#|1001,18.16,8.8,32,188
+ |1001,11.8,8.8,30.8,145.5
+ |1001,15.38,8.8,40.7,173.3
+ |1001,9,8.9,38.6,145.5
+ |2001,11.4,8.85,41,142</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -148,13 +151,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,9 +222,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -230,23 +229,23 @@
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
   <Schema ID="Schema3">
-    <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
-      <xsd:element nillable="true" name="root">
+    <xsd:schema xmlns="" xmlns:xsd="http://www.w3.org/2001/XMLSchema">
+      <xsd:element name="root" nillable="true">
         <xsd:complexType>
           <xsd:sequence minOccurs="0">
-            <xsd:element minOccurs="0" maxOccurs="unbounded" nillable="true" name="item" form="unqualified">
+            <xsd:element form="unqualified" maxOccurs="unbounded" minOccurs="0" name="item" nillable="true">
               <xsd:complexType>
                 <xsd:sequence minOccurs="0">
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="mapName" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="sceneName" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="power" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="mainCamPos" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="mainCamRote" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="playerBornPos" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="playerBornRote" form="unqualified"/>
-                  <xsd:element minOccurs="0" nillable="true" type="xsd:string" name="monsterLst" form="unqualified"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="mapName" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="sceneName" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="power" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="mainCamPos" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="mainCamRote" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="playerBornPos" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="playerBornRote" nillable="true" type="xsd:string"/>
+                  <xsd:element form="unqualified" minOccurs="0" name="monsterLst" nillable="true" type="xsd:string"/>
                 </xsd:sequence>
-                <xsd:attribute name="ID" form="unqualified" type="xsd:string"/>
+                <xsd:attribute form="unqualified" name="ID" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
           </xsd:sequence>
@@ -339,7 +338,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,7 +373,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -584,255 +583,255 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.25" customWidth="1"/>
-    <col min="9" max="9" width="44.5" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="20.26953125" customWidth="1"/>
+    <col min="9" max="9" width="44.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="140" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>